--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -176,12 +176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'bodywash'!$A$2:$A$8</f>
+              <f>'bodywash'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'bodywash'!$B$2:$B$8</f>
+              <f>'bodywash'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -626,10 +626,6 @@
       <c r="B4" t="n">
         <v>68.7</v>
       </c>
-      <c r="C4">
-        <f>AVERAGE(B2:B4)</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -641,11 +637,7 @@
         <v>70.40000000000001</v>
       </c>
       <c r="C5">
-        <f>AVERAGE(B3:B5)</f>
-        <v/>
-      </c>
-      <c r="D5" s="2">
-        <f>IF(C2=0,"",(C5-C2)/C2)</f>
+        <f>AVERAGE(B2:B5)</f>
         <v/>
       </c>
     </row>
@@ -659,11 +651,11 @@
         <v>55.3</v>
       </c>
       <c r="C6">
-        <f>AVERAGE(B4:B6)</f>
+        <f>AVERAGE(B3:B6)</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>IF(C3=0,"",(C6-C3)/C3)</f>
+        <f>IF(C2=0,"",(C6-C2)/C2)</f>
         <v/>
       </c>
     </row>
@@ -677,11 +669,11 @@
         <v>70.40000000000001</v>
       </c>
       <c r="C7">
-        <f>AVERAGE(B5:B7)</f>
+        <f>AVERAGE(B4:B7)</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>IF(C4=0,"",(C7-C4)/C4)</f>
+        <f>IF(C3=0,"",(C7-C3)/C3)</f>
         <v/>
       </c>
     </row>
@@ -695,11 +687,29 @@
         <v>68.59999999999999</v>
       </c>
       <c r="C8">
-        <f>AVERAGE(B6:B8)</f>
+        <f>AVERAGE(B5:B8)</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>IF(C5=0,"",(C8-C5)/C5)</f>
+        <f>IF(C4=0,"",(C8-C4)/C4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="C9">
+        <f>AVERAGE(B6:B9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="2">
+        <f>IF(C5=0,"",(C9-C5)/C5)</f>
         <v/>
       </c>
     </row>

--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -176,12 +176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'bodywash'!$A$2:$A$9</f>
+              <f>'bodywash'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'bodywash'!$B$2:$B$9</f>
+              <f>'bodywash'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -713,6 +713,24 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="C10">
+        <f>AVERAGE(B7:B10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="2">
+        <f>IF(C6=0,"",(C10-C6)/C6)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -176,12 +176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'bodywash'!$A$2:$A$10</f>
+              <f>'bodywash'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'bodywash'!$B$2:$B$10</f>
+              <f>'bodywash'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -636,10 +636,6 @@
       <c r="B5" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="C5">
-        <f>AVERAGE(B2:B5)</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -651,11 +647,7 @@
         <v>55.3</v>
       </c>
       <c r="C6">
-        <f>AVERAGE(B3:B6)</f>
-        <v/>
-      </c>
-      <c r="D6" s="2">
-        <f>IF(C2=0,"",(C6-C2)/C2)</f>
+        <f>AVERAGE(B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -669,11 +661,11 @@
         <v>70.40000000000001</v>
       </c>
       <c r="C7">
-        <f>AVERAGE(B4:B7)</f>
+        <f>AVERAGE(B3:B7)</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>IF(C3=0,"",(C7-C3)/C3)</f>
+        <f>IF(C2=0,"",(C7-C2)/C2)</f>
         <v/>
       </c>
     </row>
@@ -687,11 +679,11 @@
         <v>68.59999999999999</v>
       </c>
       <c r="C8">
-        <f>AVERAGE(B5:B8)</f>
+        <f>AVERAGE(B4:B8)</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>IF(C4=0,"",(C8-C4)/C4)</f>
+        <f>IF(C3=0,"",(C8-C3)/C3)</f>
         <v/>
       </c>
     </row>
@@ -705,11 +697,11 @@
         <v>72.09999999999999</v>
       </c>
       <c r="C9">
-        <f>AVERAGE(B6:B9)</f>
+        <f>AVERAGE(B5:B9)</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>IF(C5=0,"",(C9-C5)/C5)</f>
+        <f>IF(C4=0,"",(C9-C4)/C4)</f>
         <v/>
       </c>
     </row>
@@ -723,11 +715,29 @@
         <v>59.1</v>
       </c>
       <c r="C10">
-        <f>AVERAGE(B7:B10)</f>
+        <f>AVERAGE(B6:B10)</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>IF(C6=0,"",(C10-C6)/C6)</f>
+        <f>IF(C5=0,"",(C10-C5)/C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="C11">
+        <f>AVERAGE(B7:B11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="2">
+        <f>IF(C6=0,"",(C11-C6)/C6)</f>
         <v/>
       </c>
     </row>

--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -176,12 +176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'bodywash'!$A$2:$A$11</f>
+              <f>'bodywash'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'bodywash'!$B$2:$B$11</f>
+              <f>'bodywash'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -741,6 +741,24 @@
         <v/>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="C12">
+        <f>AVERAGE(B8:B12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="2">
+        <f>IF(C7=0,"",(C12-C7)/C7)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -176,12 +176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'bodywash'!$A$2:$A$12</f>
+              <f>'bodywash'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'bodywash'!$B$2:$B$12</f>
+              <f>'bodywash'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -646,10 +646,6 @@
       <c r="B6" t="n">
         <v>55.3</v>
       </c>
-      <c r="C6">
-        <f>AVERAGE(B2:B6)</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -661,11 +657,7 @@
         <v>70.40000000000001</v>
       </c>
       <c r="C7">
-        <f>AVERAGE(B3:B7)</f>
-        <v/>
-      </c>
-      <c r="D7" s="2">
-        <f>IF(C2=0,"",(C7-C2)/C2)</f>
+        <f>AVERAGE(B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -679,11 +671,11 @@
         <v>68.59999999999999</v>
       </c>
       <c r="C8">
-        <f>AVERAGE(B4:B8)</f>
+        <f>AVERAGE(B3:B8)</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>IF(C3=0,"",(C8-C3)/C3)</f>
+        <f>IF(C2=0,"",(C8-C2)/C2)</f>
         <v/>
       </c>
     </row>
@@ -697,11 +689,11 @@
         <v>72.09999999999999</v>
       </c>
       <c r="C9">
-        <f>AVERAGE(B5:B9)</f>
+        <f>AVERAGE(B4:B9)</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>IF(C4=0,"",(C9-C4)/C4)</f>
+        <f>IF(C3=0,"",(C9-C3)/C3)</f>
         <v/>
       </c>
     </row>
@@ -715,11 +707,11 @@
         <v>59.1</v>
       </c>
       <c r="C10">
-        <f>AVERAGE(B6:B10)</f>
+        <f>AVERAGE(B5:B10)</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>IF(C5=0,"",(C10-C5)/C5)</f>
+        <f>IF(C4=0,"",(C10-C4)/C4)</f>
         <v/>
       </c>
     </row>
@@ -733,11 +725,11 @@
         <v>68.59999999999999</v>
       </c>
       <c r="C11">
-        <f>AVERAGE(B7:B11)</f>
+        <f>AVERAGE(B6:B11)</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>IF(C6=0,"",(C11-C6)/C6)</f>
+        <f>IF(C5=0,"",(C11-C5)/C5)</f>
         <v/>
       </c>
     </row>
@@ -751,11 +743,29 @@
         <v>69.59999999999999</v>
       </c>
       <c r="C12">
-        <f>AVERAGE(B8:B12)</f>
+        <f>AVERAGE(B7:B12)</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>IF(C7=0,"",(C12-C7)/C7)</f>
+        <f>IF(C6=0,"",(C12-C6)/C6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="C13">
+        <f>AVERAGE(B8:B13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="2">
+        <f>IF(C7=0,"",(C13-C7)/C7)</f>
         <v/>
       </c>
     </row>

--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -176,12 +176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'bodywash'!$A$2:$A$13</f>
+              <f>'bodywash'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'bodywash'!$B$2:$B$13</f>
+              <f>'bodywash'!$B$2:$B$14</f>
             </numRef>
           </val>
         </ser>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -769,6 +769,24 @@
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="C14">
+        <f>AVERAGE(B9:B14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="2">
+        <f>IF(C8=0,"",(C14-C8)/C8)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -176,12 +176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'bodywash'!$A$2:$A$14</f>
+              <f>'bodywash'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'bodywash'!$B$2:$B$14</f>
+              <f>'bodywash'!$B$2:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -656,10 +656,6 @@
       <c r="B7" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="C7">
-        <f>AVERAGE(B2:B7)</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -671,11 +667,7 @@
         <v>68.59999999999999</v>
       </c>
       <c r="C8">
-        <f>AVERAGE(B3:B8)</f>
-        <v/>
-      </c>
-      <c r="D8" s="2">
-        <f>IF(C2=0,"",(C8-C2)/C2)</f>
+        <f>AVERAGE(B2:B8)</f>
         <v/>
       </c>
     </row>
@@ -689,11 +681,11 @@
         <v>72.09999999999999</v>
       </c>
       <c r="C9">
-        <f>AVERAGE(B4:B9)</f>
+        <f>AVERAGE(B3:B9)</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>IF(C3=0,"",(C9-C3)/C3)</f>
+        <f>IF(C2=0,"",(C9-C2)/C2)</f>
         <v/>
       </c>
     </row>
@@ -707,11 +699,11 @@
         <v>59.1</v>
       </c>
       <c r="C10">
-        <f>AVERAGE(B5:B10)</f>
+        <f>AVERAGE(B4:B10)</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>IF(C4=0,"",(C10-C4)/C4)</f>
+        <f>IF(C3=0,"",(C10-C3)/C3)</f>
         <v/>
       </c>
     </row>
@@ -725,11 +717,11 @@
         <v>68.59999999999999</v>
       </c>
       <c r="C11">
-        <f>AVERAGE(B6:B11)</f>
+        <f>AVERAGE(B5:B11)</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>IF(C5=0,"",(C11-C5)/C5)</f>
+        <f>IF(C4=0,"",(C11-C4)/C4)</f>
         <v/>
       </c>
     </row>
@@ -743,11 +735,11 @@
         <v>69.59999999999999</v>
       </c>
       <c r="C12">
-        <f>AVERAGE(B7:B12)</f>
+        <f>AVERAGE(B6:B12)</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>IF(C6=0,"",(C12-C6)/C6)</f>
+        <f>IF(C5=0,"",(C12-C5)/C5)</f>
         <v/>
       </c>
     </row>
@@ -761,11 +753,11 @@
         <v>62.1</v>
       </c>
       <c r="C13">
-        <f>AVERAGE(B8:B13)</f>
+        <f>AVERAGE(B7:B13)</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>IF(C7=0,"",(C13-C7)/C7)</f>
+        <f>IF(C6=0,"",(C13-C6)/C6)</f>
         <v/>
       </c>
     </row>
@@ -779,11 +771,29 @@
         <v>54.3</v>
       </c>
       <c r="C14">
-        <f>AVERAGE(B9:B14)</f>
+        <f>AVERAGE(B8:B14)</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>IF(C8=0,"",(C14-C8)/C8)</f>
+        <f>IF(C7=0,"",(C14-C7)/C7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="C15">
+        <f>AVERAGE(B9:B15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="2">
+        <f>IF(C8=0,"",(C15-C8)/C8)</f>
         <v/>
       </c>
     </row>
